--- a/data/comparing_check_usual.xlsx
+++ b/data/comparing_check_usual.xlsx
@@ -457,75 +457,78 @@
         <v>140</v>
       </c>
       <c r="G2" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>201</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="J2" s="1" t="n">
         <v>211</v>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="K2" s="1" t="n">
         <v>214</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="L2" s="1" t="n">
         <v>223</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>229</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="N2" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="N2" s="1" t="n">
+      <c r="O2" s="1" t="n">
         <v>354</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="P2" s="1" t="n">
         <v>408</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>456</v>
       </c>
-      <c r="Q2" s="1" t="n">
+      <c r="R2" s="1" t="n">
         <v>470</v>
       </c>
-      <c r="R2" s="1" t="n">
+      <c r="S2" s="1" t="n">
         <v>471</v>
       </c>
-      <c r="S2" s="1" t="n">
+      <c r="T2" s="1" t="n">
         <v>474</v>
       </c>
-      <c r="T2" s="1" t="n">
+      <c r="U2" s="1" t="n">
         <v>491</v>
       </c>
-      <c r="U2" s="1" t="n">
+      <c r="V2" s="1" t="n">
         <v>497</v>
       </c>
-      <c r="V2" s="1" t="n">
+      <c r="W2" s="1" t="n">
         <v>503</v>
       </c>
-      <c r="W2" s="1" t="n">
+      <c r="X2" s="1" t="n">
         <v>512</v>
       </c>
-      <c r="X2" s="1" t="n">
+      <c r="Y2" s="1" t="n">
         <v>526</v>
       </c>
-      <c r="Y2" s="1" t="n">
+      <c r="Z2" s="1" t="n">
         <v>566</v>
       </c>
-      <c r="Z2" s="1" t="n">
+      <c r="AA2" s="1" t="n">
         <v>581</v>
       </c>
-      <c r="AA2" s="1" t="n">
+      <c r="AB2" s="1" t="n">
         <v>583</v>
       </c>
-      <c r="AB2" s="1" t="n">
+      <c r="AC2" s="1" t="n">
         <v>584</v>
       </c>
-      <c r="AC2" s="1" t="n">
+      <c r="AD2" s="1" t="n">
         <v>687</v>
       </c>
-      <c r="AD2" s="1" t="n">
+      <c r="AE2" s="1" t="n">
         <v>727</v>
       </c>
     </row>
@@ -680,6 +683,11 @@
           <t>Cat 3</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Cat 3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -714,120 +722,125 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Brevibacterium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>Bulleidia</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Cellulosimicrobium</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Clavibacter</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Clostridium</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Cohnella</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Corynebacterium</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Enterococcus</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Halomonas</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Legionella</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Methyloversatilis</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Mycobacterium</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Mycoplana</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Neisseria</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Novosphingobium</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Oerskovia</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Opitutus</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Oxobacter</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Paracoccus</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Prevotella</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Psb-m-3</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>Pseudarthrobacter</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Pseudoalteromonas</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>Streptococcus</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>Thiobacillus</t>
         </is>
@@ -864,6 +877,7 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -898,120 +912,125 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>2/17 (11.8%)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>0/17 (0.0%)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0/17 (0.0%)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>0/17 (0.0%)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>4/17 (23.5%)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0/17 (0.0%)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>6/17 (35.3%)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>3/17 (17.6%)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>4/17 (23.5%)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>8/17 (47.1%)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3/17 (17.6%)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>7/17 (41.2%)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3/17 (17.6%)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>6/17 (35.3%)</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>16/17 (94.1%)</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0/17 (0.0%)</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>1/17 (5.9%)</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1/17 (5.9%)</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>13/17 (76.5%)</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2/17 (11.8%)</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>3/17 (17.6%)</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0/17 (0.0%)</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>3/17 (17.6%)</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>14/17 (82.4%)</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>7/17 (41.2%)</t>
         </is>
@@ -1050,120 +1069,125 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>0.0022</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.0743</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0.1092</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>0.0066</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.0462</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.1253</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.0519</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.0069</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.0366</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.0155</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1.1462</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>0.0004</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>0.0007</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>0.2201</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.0014</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.1153</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.0255</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.6624</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.0095</t>
         </is>
@@ -1202,120 +1226,125 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>8/32 (25.0%)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>1/32 (3.1%)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0/32 (0.0%)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>0/32 (0.0%)</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>8/32 (25.0%)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1/32 (3.1%)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>12/32 (37.5%)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>3/32 (9.4%)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>11/32 (34.4%)</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>14/32 (43.8%)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4/32 (12.5%)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>9/32 (28.1%)</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>6/32 (18.8%)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>7/32 (21.9%)</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>24/32 (75.0%)</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>1/32 (3.1%)</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>4/32 (12.5%)</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>4/32 (12.5%)</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>18/32 (56.2%)</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>7/32 (21.9%)</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>8/32 (25.0%)</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0/32 (0.0%)</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>7/32 (21.9%)</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>22/32 (68.8%)</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>11/32 (34.4%)</t>
         </is>
@@ -1354,120 +1383,125 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>0.0147</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>0.0008</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>0.2834</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>0.0005</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>0.1405</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>0.0047</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>1.6274</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.1243</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.0213</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.0182</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.0369</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.0138</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1.5058</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0.0005</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>0.0135</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>0.0128</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>0.0460</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.0358</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.8370</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.0000</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.0225</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.5722</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.0263</t>
         </is>
@@ -1506,120 +1540,125 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>4/21 (19.0%)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>6/21 (28.6%)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>3/21 (14.3%)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>3/21 (14.3%)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>11/21 (52.4%)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>3/21 (14.3%)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>13/21 (61.9%)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>9/21 (42.9%)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>13/21 (61.9%)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>13/21 (61.9%)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>9/21 (42.9%)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>11/21 (52.4%)</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>9/21 (42.9%)</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>10/21 (47.6%)</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>20/21 (95.2%)</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>5/21 (23.8%)</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>3/21 (14.3%)</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>6/21 (28.6%)</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>15/21 (71.4%)</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>10/21 (47.6%)</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>9/21 (42.9%)</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>4/21 (19.0%)</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>9/21 (42.9%)</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>14/21 (66.7%)</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>10/21 (47.6%)</t>
         </is>
@@ -1658,120 +1697,125 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>0.0358</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>0.0169</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.0019</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>0.0009</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1.5101</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.0082</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1.1856</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>0.0200</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>2.7596</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.4315</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.0309</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.0762</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.4448</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.1514</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>4.9482</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0.0132</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>0.7871</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>0.0085</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>0.4884</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>0.1763</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>0.8108</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>0.4952</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>0.2507</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>1.4245</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>0.0225</t>
         </is>
